--- a/data/processed/Data_Set_AB_processed.xlsx
+++ b/data/processed/Data_Set_AB_processed.xlsx
@@ -553,16 +553,16 @@
         <v>265.235294117647</v>
       </c>
       <c r="M2" t="n">
-        <v>10.01973008185145</v>
+        <v>10.01973852982916</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.053009266481469</v>
+        <v>-1.052996176320649</v>
       </c>
       <c r="O2" t="n">
-        <v>-37.12314161196046</v>
+        <v>-37.12251587073171</v>
       </c>
       <c r="P2" t="n">
-        <v>-18.23436362831105</v>
+        <v>-18.23405627304405</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -606,16 +606,16 @@
         <v>263.647058823529</v>
       </c>
       <c r="M3" t="n">
-        <v>10.52202330714203</v>
+        <v>10.52203245396588</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.477955877542994</v>
+        <v>-1.477904304379286</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.82364702034395</v>
+        <v>-11.82323443503429</v>
       </c>
       <c r="P3" t="n">
-        <v>-16.93491109684835</v>
+        <v>-16.93432015434752</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>268.411764705882</v>
       </c>
       <c r="M4" t="n">
-        <v>11.55563586892077</v>
+        <v>11.55564663993898</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>55.03415464808823</v>
+        <v>55.03871559624276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -712,16 +712,16 @@
         <v>162</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.82516887028922</v>
+        <v>-5.825097707372331</v>
       </c>
       <c r="N5" t="n">
-        <v>10.30671132864137</v>
+        <v>10.30672002246378</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.82260347685709</v>
+        <v>-11.82301601813115</v>
       </c>
       <c r="P5" t="n">
-        <v>-119.3959799043123</v>
+        <v>-119.4001461414498</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -765,16 +765,16 @@
         <v>169.941176470588</v>
       </c>
       <c r="M6" t="n">
-        <v>-7.581752142972658</v>
+        <v>-7.581578013597992</v>
       </c>
       <c r="N6" t="n">
-        <v>12.59407135662521</v>
+        <v>12.59408381909858</v>
       </c>
       <c r="O6" t="n">
-        <v>-87.36463032539453</v>
+        <v>-87.3581946037342</v>
       </c>
       <c r="P6" t="n">
-        <v>106.7789926199313</v>
+        <v>106.771126737902</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -818,16 +818,16 @@
         <v>149.294117647059</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.020331520438788</v>
+        <v>-7.019995612839079</v>
       </c>
       <c r="N7" t="n">
-        <v>11.14486953296912</v>
+        <v>11.144879645698</v>
       </c>
       <c r="O7" t="n">
-        <v>-72.57450496519783</v>
+        <v>-72.57672576503693</v>
       </c>
       <c r="P7" t="n">
-        <v>-72.43050793153701</v>
+        <v>-72.43272432502721</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -871,16 +871,16 @@
         <v>446.294117647059</v>
       </c>
       <c r="M8" t="n">
-        <v>15.75547756651901</v>
+        <v>15.755496958564</v>
       </c>
       <c r="N8" t="n">
-        <v>15.55782318545192</v>
+        <v>15.55784177072952</v>
       </c>
       <c r="O8" t="n">
-        <v>-22.09603716055638</v>
+        <v>-22.09579700158421</v>
       </c>
       <c r="P8" t="n">
-        <v>43.67419845016171</v>
+        <v>43.6737237609433</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -924,16 +924,16 @@
         <v>462.176470588235</v>
       </c>
       <c r="M9" t="n">
-        <v>20.71566331617952</v>
+        <v>20.71569572599246</v>
       </c>
       <c r="N9" t="n">
-        <v>20.23903330930092</v>
+        <v>20.23906348575003</v>
       </c>
       <c r="O9" t="n">
-        <v>-32.23155714979929</v>
+        <v>-32.23099968380873</v>
       </c>
       <c r="P9" t="n">
-        <v>55.62181921094391</v>
+        <v>55.62085719497929</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -977,16 +977,16 @@
         <v>454.235294117647</v>
       </c>
       <c r="M10" t="n">
-        <v>17.8782457418339</v>
+        <v>17.87827035868506</v>
       </c>
       <c r="N10" t="n">
-        <v>18.25774329092933</v>
+        <v>18.25776819805968</v>
       </c>
       <c r="O10" t="n">
-        <v>-23.31204735406775</v>
+        <v>-23.31175573312167</v>
       </c>
       <c r="P10" t="n">
-        <v>53.18060802646747</v>
+        <v>53.17994276618423</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1030,16 +1030,16 @@
         <v>164.076923076923</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.911087375003969</v>
+        <v>-9.910575410355266</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7454951900028877</v>
+        <v>0.7454851555368531</v>
       </c>
       <c r="O11" t="n">
-        <v>130.7267035939865</v>
+        <v>130.7270360943851</v>
       </c>
       <c r="P11" t="n">
-        <v>43.01013417604474</v>
+        <v>43.0102435713432</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1083,16 +1083,16 @@
         <v>162</v>
       </c>
       <c r="M12" t="n">
-        <v>4.95553231835527</v>
+        <v>4.95527633720545</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.572240051921033</v>
+        <v>-2.572210186517972</v>
       </c>
       <c r="O12" t="n">
-        <v>132.6208118070679</v>
+        <v>132.6211525438276</v>
       </c>
       <c r="P12" t="n">
-        <v>43.86898187412805</v>
+        <v>43.86909458475417</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1136,16 +1136,16 @@
         <v>172.384615384615</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.105589479958427</v>
+        <v>-5.105453617325849</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.433573371191902</v>
+        <v>-4.433691677678066</v>
       </c>
       <c r="O13" t="n">
-        <v>146.9716451850126</v>
+        <v>146.9720415393413</v>
       </c>
       <c r="P13" t="n">
-        <v>42.33981591895483</v>
+        <v>42.33993010131496</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1189,16 +1189,16 @@
         <v>356.4</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.658352259984703</v>
+        <v>-7.658175900676842</v>
       </c>
       <c r="N14" t="n">
-        <v>-63.20532953580693</v>
+        <v>-63.17759927894203</v>
       </c>
       <c r="O14" t="n">
-        <v>281.9356724348614</v>
+        <v>281.9363874593784</v>
       </c>
       <c r="P14" t="n">
-        <v>93.08415158979372</v>
+        <v>93.08438766297293</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1242,16 +1242,16 @@
         <v>365.4</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.02010619370435</v>
+        <v>-7.020007400356605</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.632571774601332</v>
+        <v>-2.63249958463078</v>
       </c>
       <c r="O15" t="n">
-        <v>285.5669421787376</v>
+        <v>285.5676632862189</v>
       </c>
       <c r="P15" t="n">
-        <v>84.28191001803029</v>
+        <v>84.28212284489108</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1295,16 +1295,16 @@
         <v>351</v>
       </c>
       <c r="M16" t="n">
-        <v>-42.14635812340187</v>
+        <v>-42.1271286654951</v>
       </c>
       <c r="N16" t="n">
-        <v>-118.5271903786999</v>
+        <v>-118.4650132973987</v>
       </c>
       <c r="O16" t="n">
-        <v>291.5322324839208</v>
+        <v>291.5329904674625</v>
       </c>
       <c r="P16" t="n">
-        <v>99.17594027083638</v>
+        <v>99.17619812819169</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1348,16 +1348,16 @@
         <v>762.75</v>
       </c>
       <c r="M17" t="n">
-        <v>-42.12441112687939</v>
+        <v>-42.12061707083398</v>
       </c>
       <c r="N17" t="n">
-        <v>1.504312466871249</v>
+        <v>1.504287323361122</v>
       </c>
       <c r="O17" t="n">
-        <v>536.2538218436929</v>
+        <v>536.2550140846266</v>
       </c>
       <c r="P17" t="n">
-        <v>170.2597547074156</v>
+        <v>170.2601332420585</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1401,16 +1401,16 @@
         <v>761.0625</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.973210428138871</v>
+        <v>-2.973172622990889</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.034798061364947</v>
+        <v>-2.034779659757985</v>
       </c>
       <c r="O18" t="n">
-        <v>616.3775967040602</v>
+        <v>616.3791730128039</v>
       </c>
       <c r="P18" t="n">
-        <v>190.1341522319937</v>
+        <v>190.1346384763482</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1454,16 +1454,16 @@
         <v>754.3125</v>
       </c>
       <c r="M19" t="n">
-        <v>1.684874525350038</v>
+        <v>1.684801684874509</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3074490638034288</v>
+        <v>0.3074448627571754</v>
       </c>
       <c r="O19" t="n">
-        <v>547.8648487478241</v>
+        <v>547.8660903970033</v>
       </c>
       <c r="P19" t="n">
-        <v>169.4881803326136</v>
+        <v>169.4885644508145</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1507,16 +1507,16 @@
         <v>302.4</v>
       </c>
       <c r="M20" t="n">
-        <v>27.82622101604218</v>
+        <v>27.82627763229773</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.428437711726434</v>
+        <v>-3.42836774783642</v>
       </c>
       <c r="O20" t="n">
-        <v>-27.42750169381146</v>
+        <v>-27.42694198269135</v>
       </c>
       <c r="P20" t="n">
-        <v>-34.82857357944329</v>
+        <v>-34.82786283516378</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1560,16 +1560,16 @@
         <v>306</v>
       </c>
       <c r="M21" t="n">
-        <v>30.29360109191609</v>
+        <v>30.29366738774701</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.932139607391386</v>
+        <v>-1.932108498227868</v>
       </c>
       <c r="O21" t="n">
-        <v>-27.79099243756935</v>
+        <v>-27.79048962213016</v>
       </c>
       <c r="P21" t="n">
-        <v>-8.708809141499616</v>
+        <v>-8.708651575205314</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         <v>291.6</v>
       </c>
       <c r="M22" t="n">
-        <v>26.18265598588313</v>
+        <v>26.18270720122472</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9795518550263396</v>
+        <v>-0.9795318654159995</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.836414840210623</v>
+        <v>-7.836254923327902</v>
       </c>
       <c r="P22" t="n">
-        <v>-8.04048814334109</v>
+        <v>-8.040324061956214</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -1666,16 +1666,16 @@
         <v>170.4375</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.66858373263146</v>
+        <v>-0.668572262706393</v>
       </c>
       <c r="N23" t="n">
-        <v>39.23239944762177</v>
+        <v>39.23250890070062</v>
       </c>
       <c r="O23" t="n">
-        <v>-84.23676913700918</v>
+        <v>-84.24035304007732</v>
       </c>
       <c r="P23" t="n">
-        <v>2.313320364558017</v>
+        <v>2.313418786138487</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -1719,16 +1719,16 @@
         <v>170.4375</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.755081647839187</v>
+        <v>-1.75500261064543</v>
       </c>
       <c r="N24" t="n">
-        <v>43.30148617272611</v>
+        <v>43.30161993570966</v>
       </c>
       <c r="O24" t="n">
-        <v>-66.068244367166</v>
+        <v>-66.07066946092728</v>
       </c>
       <c r="P24" t="n">
-        <v>4.978058231357686</v>
+        <v>4.978240955419385</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>173.8125</v>
       </c>
       <c r="M25" t="n">
-        <v>28.06995189565663</v>
+        <v>28.08006457403213</v>
       </c>
       <c r="N25" t="n">
-        <v>46.20560062971572</v>
+        <v>46.20575318151588</v>
       </c>
       <c r="O25" t="n">
-        <v>-26.74210085077642</v>
+        <v>-26.74289547354601</v>
       </c>
       <c r="P25" t="n">
-        <v>15.04243172856173</v>
+        <v>15.04287870386963</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -1825,16 +1825,16 @@
         <v>496.8</v>
       </c>
       <c r="M26" t="n">
-        <v>43.00528078698576</v>
+        <v>43.00541164299647</v>
       </c>
       <c r="N26" t="n">
-        <v>60.0579166878834</v>
+        <v>60.05816469150307</v>
       </c>
       <c r="O26" t="n">
-        <v>-45.12940072160389</v>
+        <v>-45.12869355880562</v>
       </c>
       <c r="P26" t="n">
-        <v>-9.245259175606352</v>
+        <v>-9.245114305449761</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -1878,16 +1878,16 @@
         <v>495</v>
       </c>
       <c r="M27" t="n">
-        <v>46.63275036449919</v>
+        <v>46.63290377560751</v>
       </c>
       <c r="N27" t="n">
-        <v>71.72072052825892</v>
+        <v>71.72107016676391</v>
       </c>
       <c r="O27" t="n">
-        <v>-21.84037595780493</v>
+        <v>-21.84002105170842</v>
       </c>
       <c r="P27" t="n">
-        <v>-23.18373241552717</v>
+        <v>-23.18335567988902</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -1931,16 +1931,16 @@
         <v>504</v>
       </c>
       <c r="M28" t="n">
-        <v>47.8192932338779</v>
+        <v>47.81945314438936</v>
       </c>
       <c r="N28" t="n">
-        <v>91.12949333811125</v>
+        <v>91.13006699585912</v>
       </c>
       <c r="O28" t="n">
-        <v>-45.5358974306722</v>
+        <v>-45.53517747126341</v>
       </c>
       <c r="P28" t="n">
-        <v>-10.68828693040338</v>
+        <v>-10.68811793993271</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -1984,16 +1984,16 @@
         <v>183.6</v>
       </c>
       <c r="M29" t="n">
-        <v>-15.16382738802587</v>
+        <v>-15.16321279836604</v>
       </c>
       <c r="N29" t="n">
-        <v>-11.59856944194081</v>
+        <v>-11.59827443479845</v>
       </c>
       <c r="O29" t="n">
-        <v>283.8073530841486</v>
+        <v>283.8088354706663</v>
       </c>
       <c r="P29" t="n">
-        <v>111.5708603279498</v>
+        <v>111.5714430864207</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2037,16 +2037,16 @@
         <v>172.8</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.063220226478254</v>
+        <v>-3.063276659349609</v>
       </c>
       <c r="N30" t="n">
-        <v>-28.06361085125792</v>
+        <v>-28.0800280635963</v>
       </c>
       <c r="O30" t="n">
-        <v>303.9839718582974</v>
+        <v>303.9856033317911</v>
       </c>
       <c r="P30" t="n">
-        <v>105.5106326051002</v>
+        <v>105.5111988777209</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2090,16 +2090,16 @@
         <v>176.4</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.959118246493632</v>
+        <v>-1.959072081926664</v>
       </c>
       <c r="N31" t="n">
-        <v>2.514692908263295</v>
+        <v>2.514627038383535</v>
       </c>
       <c r="O31" t="n">
-        <v>268.2850359790545</v>
+        <v>268.2863154360335</v>
       </c>
       <c r="P31" t="n">
-        <v>85.78482699074289</v>
+        <v>85.78523610038698</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2143,16 +2143,16 @@
         <v>356.4</v>
       </c>
       <c r="M32" t="n">
-        <v>-5.523845016936988</v>
+        <v>-5.52393677154698</v>
       </c>
       <c r="N32" t="n">
-        <v>-18.72356434253231</v>
+        <v>-18.71991326805254</v>
       </c>
       <c r="O32" t="n">
-        <v>467.8692419079501</v>
+        <v>467.8711295173922</v>
       </c>
       <c r="P32" t="n">
-        <v>162.3470120582912</v>
+        <v>162.3476670441834</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -2196,16 +2196,16 @@
         <v>370.8</v>
       </c>
       <c r="M33" t="n">
-        <v>-5.205905117755083</v>
+        <v>-5.205845849442327</v>
       </c>
       <c r="N33" t="n">
-        <v>-2.808115488429579</v>
+        <v>-2.808005971802137</v>
       </c>
       <c r="O33" t="n">
-        <v>534.8551061628574</v>
+        <v>534.8575894182975</v>
       </c>
       <c r="P33" t="n">
-        <v>201.7220889979499</v>
+        <v>201.7230255646371</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2249,16 +2249,16 @@
         <v>365.4</v>
       </c>
       <c r="M34" t="n">
-        <v>6.793332282492061</v>
+        <v>6.793554325756043</v>
       </c>
       <c r="N34" t="n">
-        <v>42.14354559893586</v>
+        <v>42.11889229778185</v>
       </c>
       <c r="O34" t="n">
-        <v>505.4382400187851</v>
+        <v>505.4404465959193</v>
       </c>
       <c r="P34" t="n">
-        <v>165.7465124080396</v>
+        <v>165.7472360028043</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -2302,16 +2302,16 @@
         <v>770.4</v>
       </c>
       <c r="M35" t="n">
-        <v>-6.793635438738527</v>
+        <v>-6.793524412641003</v>
       </c>
       <c r="N35" t="n">
-        <v>-2.755544996682936</v>
+        <v>-2.755522398592562</v>
       </c>
       <c r="O35" t="n">
-        <v>579.3496016897101</v>
+        <v>579.3509869182984</v>
       </c>
       <c r="P35" t="n">
-        <v>191.3966057065741</v>
+        <v>191.3970633370776</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -2355,16 +2355,16 @@
         <v>777.6</v>
       </c>
       <c r="M36" t="n">
-        <v>48.12939299543384</v>
+        <v>48.13635960283705</v>
       </c>
       <c r="N36" t="n">
-        <v>-12.03710772821218</v>
+        <v>-12.03408990546744</v>
       </c>
       <c r="O36" t="n">
-        <v>902.5432024271762</v>
+        <v>902.5465092373955</v>
       </c>
       <c r="P36" t="n">
-        <v>314.0230124449062</v>
+        <v>314.0241629876214</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -2408,16 +2408,16 @@
         <v>778.95</v>
       </c>
       <c r="M37" t="n">
-        <v>-25.74140784010036</v>
+        <v>-25.73995881751502</v>
       </c>
       <c r="N37" t="n">
-        <v>39.10645646482142</v>
+        <v>39.11135872481419</v>
       </c>
       <c r="O37" t="n">
-        <v>934.1794794818037</v>
+        <v>991.7021157320429</v>
       </c>
       <c r="P37" t="n">
-        <v>344.0153310954266</v>
+        <v>375.9440407122832</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -2461,16 +2461,16 @@
         <v>267.923076923077</v>
       </c>
       <c r="M38" t="n">
-        <v>16.80842287037777</v>
+        <v>16.80844596942876</v>
       </c>
       <c r="N38" t="n">
-        <v>-14.04183948097142</v>
+        <v>-14.03946650264498</v>
       </c>
       <c r="O38" t="n">
-        <v>-112.3347158477713</v>
+        <v>-112.3157320211599</v>
       </c>
       <c r="P38" t="n">
-        <v>-141.4585310675695</v>
+        <v>-141.4346255081328</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>272.076923076923</v>
       </c>
       <c r="M39" t="n">
-        <v>19.00533124840178</v>
+        <v>19.00536032419537</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.6194258129188758</v>
+        <v>-0.6194119578304484</v>
       </c>
       <c r="O39" t="n">
-        <v>-42.12199803064915</v>
+        <v>-42.11999592162622</v>
       </c>
       <c r="P39" t="n">
-        <v>-59.05123855859394</v>
+        <v>-59.04843178248975</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -2567,16 +2567,16 @@
         <v>274.153846153846</v>
       </c>
       <c r="M40" t="n">
-        <v>18.40122779111615</v>
+        <v>18.40125463332666</v>
       </c>
       <c r="N40" t="n">
-        <v>-4.513096756058456</v>
+        <v>-4.512851598741723</v>
       </c>
       <c r="O40" t="n">
-        <v>1.330174044320574e-13</v>
+        <v>1.330135136793974e-13</v>
       </c>
       <c r="P40" t="n">
-        <v>1.620046558331568</v>
+        <v>1.619999172047923</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -2620,16 +2620,16 @@
         <v>156</v>
       </c>
       <c r="M41" t="n">
-        <v>2.808230443327804</v>
+        <v>2.808002808230408</v>
       </c>
       <c r="N41" t="n">
-        <v>16.62557860486624</v>
+        <v>16.62560115054017</v>
       </c>
       <c r="O41" t="n">
-        <v>73.70630086502436</v>
+        <v>73.71115173189371</v>
       </c>
       <c r="P41" t="n">
-        <v>73.8891041905826</v>
+        <v>73.89396708837177</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -2673,16 +2673,16 @@
         <v>159</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.404058310526062</v>
+        <v>-1.404001404058323</v>
       </c>
       <c r="N42" t="n">
-        <v>23.31639002800833</v>
+        <v>23.31643178334426</v>
       </c>
       <c r="O42" t="n">
-        <v>-101.08271337409</v>
+        <v>-101.089809500493</v>
       </c>
       <c r="P42" t="n">
-        <v>28.97548458215622</v>
+        <v>28.9775186955503</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -2726,16 +2726,16 @@
         <v>162</v>
       </c>
       <c r="M43" t="n">
-        <v>-3.829235828222746</v>
+        <v>-3.829094738326738</v>
       </c>
       <c r="N43" t="n">
-        <v>20.84657459135713</v>
+        <v>20.8466088102509</v>
       </c>
       <c r="O43" t="n">
-        <v>-13.75388817961549</v>
+        <v>-13.75329705111367</v>
       </c>
       <c r="P43" t="n">
-        <v>-43.31519621577007</v>
+        <v>-43.31333457150551</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -2779,16 +2779,16 @@
         <v>460.8</v>
       </c>
       <c r="M44" t="n">
-        <v>21.23062403157922</v>
+        <v>21.23065889688994</v>
       </c>
       <c r="N44" t="n">
-        <v>30.25213348967299</v>
+        <v>30.25220027256016</v>
       </c>
       <c r="O44" t="n">
-        <v>-38.23716279366959</v>
+        <v>-38.2366868623681</v>
       </c>
       <c r="P44" t="n">
-        <v>-30.84364889411241</v>
+        <v>-30.84326498858992</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -2832,16 +2832,16 @@
         <v>469.8</v>
       </c>
       <c r="M45" t="n">
-        <v>28.02120784909316</v>
+        <v>28.02126724755521</v>
       </c>
       <c r="N45" t="n">
-        <v>48.3536046882217</v>
+        <v>48.35377440925501</v>
       </c>
       <c r="O45" t="n">
-        <v>-41.57356553344768</v>
+        <v>-41.57309175605563</v>
       </c>
       <c r="P45" t="n">
-        <v>-19.32046366073779</v>
+        <v>-19.32024348239203</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -2885,16 +2885,16 @@
         <v>457.2</v>
       </c>
       <c r="M46" t="n">
-        <v>28.68511434809118</v>
+        <v>28.68517698852161</v>
       </c>
       <c r="N46" t="n">
-        <v>38.33990654647778</v>
+        <v>38.34001437739755</v>
       </c>
       <c r="O46" t="n">
-        <v>-32.0930997049777</v>
+        <v>-32.09175865943025</v>
       </c>
       <c r="P46" t="n">
-        <v>-53.20991357335687</v>
+        <v>-53.20769013846483</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -2938,16 +2938,16 @@
         <v>150.1875</v>
       </c>
       <c r="M47" t="n">
-        <v>-3.473775011025735</v>
+        <v>-3.473813716700732</v>
       </c>
       <c r="N47" t="n">
-        <v>-2.307925976978378</v>
+        <v>-2.307945704987709</v>
       </c>
       <c r="O47" t="n">
-        <v>171.1824245925744</v>
+        <v>171.1829958107219</v>
       </c>
       <c r="P47" t="n">
-        <v>56.03262916092465</v>
+        <v>56.03281613604612</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -2991,16 +2991,16 @@
         <v>156.9375</v>
       </c>
       <c r="M48" t="n">
-        <v>-1.858225744297449</v>
+        <v>-1.858235589239335</v>
       </c>
       <c r="N48" t="n">
-        <v>-3.136668635520906</v>
+        <v>-3.136606168953582</v>
       </c>
       <c r="O48" t="n">
-        <v>178.6810346171176</v>
+        <v>178.6816483616365</v>
       </c>
       <c r="P48" t="n">
-        <v>65.10763189479938</v>
+        <v>65.10785553046556</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3044,16 +3044,16 @@
         <v>165.375</v>
       </c>
       <c r="M49" t="n">
-        <v>-2.406834596554318</v>
+        <v>-2.406859370896472</v>
       </c>
       <c r="N49" t="n">
-        <v>-6.937577221841667</v>
+        <v>-6.937424431779485</v>
       </c>
       <c r="O49" t="n">
-        <v>234.6818916250212</v>
+        <v>234.682925329559</v>
       </c>
       <c r="P49" t="n">
-        <v>95.30097743378126</v>
+        <v>95.30139720648782</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3097,16 +3097,16 @@
         <v>341.357142857143</v>
       </c>
       <c r="M50" t="n">
-        <v>-5.054353312951506</v>
+        <v>-5.054401111920408</v>
       </c>
       <c r="N50" t="n">
-        <v>-5.41549734824473</v>
+        <v>-5.415433986925755</v>
       </c>
       <c r="O50" t="n">
-        <v>323.7686403257676</v>
+        <v>323.7695839784581</v>
       </c>
       <c r="P50" t="n">
-        <v>112.7673350085253</v>
+        <v>112.7676636790196</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3150,16 +3150,16 @@
         <v>358.714285714286</v>
       </c>
       <c r="M51" t="n">
-        <v>13.16171276526813</v>
+        <v>13.16249070321275</v>
       </c>
       <c r="N51" t="n">
-        <v>-4.920595350485827</v>
+        <v>-4.920557687298391</v>
       </c>
       <c r="O51" t="n">
-        <v>358.2687450907156</v>
+        <v>358.2699048612986</v>
       </c>
       <c r="P51" t="n">
-        <v>134.1773609101942</v>
+        <v>134.1777952627806</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -3203,16 +3203,16 @@
         <v>337.5</v>
       </c>
       <c r="M52" t="n">
-        <v>-2.21683060341557</v>
+        <v>-2.216841637381825</v>
       </c>
       <c r="N52" t="n">
-        <v>-2.340023951120214</v>
+        <v>-2.339997333404721</v>
       </c>
       <c r="O52" t="n">
-        <v>295.1145530039923</v>
+        <v>295.1153428687542</v>
       </c>
       <c r="P52" t="n">
-        <v>100.3215127710247</v>
+        <v>100.3217812783788</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -3256,16 +3256,16 @@
         <v>742.5</v>
       </c>
       <c r="M53" t="n">
-        <v>11.23105307270024</v>
+        <v>11.23186229655891</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.8508956287089425</v>
+        <v>-0.850911718405333</v>
       </c>
       <c r="O53" t="n">
-        <v>625.8492565806398</v>
+        <v>625.8509113670189</v>
       </c>
       <c r="P53" t="n">
-        <v>213.0865346160504</v>
+        <v>213.0870980307886</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -3309,16 +3309,16 @@
         <v>750.9375</v>
       </c>
       <c r="M54" t="n">
-        <v>21.05622812870678</v>
+        <v>21.06002105622731</v>
       </c>
       <c r="N54" t="n">
-        <v>-35.10399015354684</v>
+        <v>-35.10033930692979</v>
       </c>
       <c r="O54" t="n">
-        <v>778.0049859967926</v>
+        <v>778.0075277500907</v>
       </c>
       <c r="P54" t="n">
-        <v>278.2346293458337</v>
+        <v>278.2355383423048</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>745.875</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.9465051449226413</v>
+        <v>-0.9465166390937111</v>
       </c>
       <c r="N55" t="n">
-        <v>-1.033607607811427</v>
+        <v>-1.033619478432406</v>
       </c>
       <c r="O55" t="n">
-        <v>793.7919689692878</v>
+        <v>793.7945990183221</v>
       </c>
       <c r="P55" t="n">
-        <v>273.2760058460901</v>
+        <v>273.276911283942</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -3415,16 +3415,16 @@
         <v>231.882352941176</v>
       </c>
       <c r="M56" t="n">
-        <v>7.228157314301915</v>
+        <v>7.228162551173946</v>
       </c>
       <c r="N56" t="n">
-        <v>-3.744032298518564</v>
+        <v>-3.743999201313203</v>
       </c>
       <c r="O56" t="n">
-        <v>-29.95225838814851</v>
+        <v>-29.95199361050562</v>
       </c>
       <c r="P56" t="n">
-        <v>-4.378437771323227</v>
+        <v>-4.37839906598029</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -3468,16 +3468,16 @@
         <v>228.705882352941</v>
       </c>
       <c r="M57" t="n">
-        <v>7.9519323961499</v>
+        <v>7.951938487935563</v>
       </c>
       <c r="N57" t="n">
-        <v>-1.341415610798598</v>
+        <v>-1.341398616736835</v>
       </c>
       <c r="O57" t="n">
-        <v>-10.73132488638878</v>
+        <v>-10.73118893389468</v>
       </c>
       <c r="P57" t="n">
-        <v>-6.975361176152951</v>
+        <v>-6.975272807031788</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -3521,16 +3521,16 @@
         <v>230.294117647059</v>
       </c>
       <c r="M58" t="n">
-        <v>8.25769061367204</v>
+        <v>8.257697068882784</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.8340769876227274</v>
+        <v>-0.83406056208046</v>
       </c>
       <c r="O58" t="n">
-        <v>-6.672615900981812</v>
+        <v>-6.672484496643673</v>
       </c>
       <c r="P58" t="n">
-        <v>-10.31011831922631</v>
+        <v>-10.30991528127328</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -3574,16 +3574,16 @@
         <v>100.8</v>
       </c>
       <c r="M59" t="n">
-        <v>-21.06190873489468</v>
+        <v>-21.05977466254519</v>
       </c>
       <c r="N59" t="n">
-        <v>5.363541432692794</v>
+        <v>5.363544578751937</v>
       </c>
       <c r="O59" t="n">
-        <v>-33.92191520620519</v>
+        <v>-33.92211498085056</v>
       </c>
       <c r="P59" t="n">
-        <v>17.49491367579288</v>
+        <v>17.49501670771646</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -3627,16 +3627,16 @@
         <v>90</v>
       </c>
       <c r="M60" t="n">
-        <v>-2.429935034297769</v>
+        <v>-2.429982382580202</v>
       </c>
       <c r="N60" t="n">
-        <v>5.390777027399363</v>
+        <v>5.390780256339951</v>
       </c>
       <c r="O60" t="n">
-        <v>-22.50942155712903</v>
+        <v>-22.50950152482982</v>
       </c>
       <c r="P60" t="n">
-        <v>16.08864695260707</v>
+        <v>16.08870410965584</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -3680,16 +3680,16 @@
         <v>97.2</v>
       </c>
       <c r="M61" t="n">
-        <v>14.03897164550992</v>
+        <v>14.03964900809478</v>
       </c>
       <c r="N61" t="n">
-        <v>5.037465068558442</v>
+        <v>5.03746803028158</v>
       </c>
       <c r="O61" t="n">
-        <v>-24.65548587731487</v>
+        <v>-24.65560314106239</v>
       </c>
       <c r="P61" t="n">
-        <v>19.97550939134306</v>
+        <v>19.97560439669406</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -3733,16 +3733,16 @@
         <v>408.176470588235</v>
       </c>
       <c r="M62" t="n">
-        <v>8.565268603660392</v>
+        <v>8.565275477109036</v>
       </c>
       <c r="N62" t="n">
-        <v>10.53501889408</v>
+        <v>10.5350289151789</v>
       </c>
       <c r="O62" t="n">
-        <v>-32.40865322139864</v>
+        <v>-32.40856829279792</v>
       </c>
       <c r="P62" t="n">
-        <v>1.458266074364687</v>
+        <v>1.458262252900823</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -3786,16 +3786,16 @@
         <v>417.705882352941</v>
       </c>
       <c r="M63" t="n">
-        <v>8.88826507884751</v>
+        <v>8.888272480466547</v>
       </c>
       <c r="N63" t="n">
-        <v>11.1427465588703</v>
+        <v>11.14275739648355</v>
       </c>
       <c r="O63" t="n">
-        <v>-26.06675743378848</v>
+        <v>-26.06670852179615</v>
       </c>
       <c r="P63" t="n">
-        <v>3.451505356345553</v>
+        <v>3.451498879897382</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -3839,16 +3839,16 @@
         <v>408.176470588235</v>
       </c>
       <c r="M64" t="n">
-        <v>9.02570704920311</v>
+        <v>9.025714842179141</v>
       </c>
       <c r="N64" t="n">
-        <v>11.68558808070011</v>
+        <v>11.68559999998803</v>
       </c>
       <c r="O64" t="n">
-        <v>-23.83536636728969</v>
+        <v>-23.83532042887904</v>
       </c>
       <c r="P64" t="n">
-        <v>2.438635514461584</v>
+        <v>2.438630814427274</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>96.1875</v>
       </c>
       <c r="M65" t="n">
-        <v>-2.276735207770236</v>
+        <v>-2.276751834033461</v>
       </c>
       <c r="N65" t="n">
-        <v>-0.8424054419391434</v>
+        <v>-0.8423896723183752</v>
       </c>
       <c r="O65" t="n">
-        <v>32.93588862388106</v>
+        <v>32.93592173660284</v>
       </c>
       <c r="P65" t="n">
-        <v>7.835594687496126</v>
+        <v>7.835602565160208</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -3945,16 +3945,16 @@
         <v>99.5625</v>
       </c>
       <c r="M66" t="n">
-        <v>-3.239889731617543</v>
+        <v>-3.239957070501474</v>
       </c>
       <c r="N66" t="n">
-        <v>-2.088625067465323</v>
+        <v>-2.088608910737305</v>
       </c>
       <c r="O66" t="n">
-        <v>31.19344164253476</v>
+        <v>31.19347218336279</v>
       </c>
       <c r="P66" t="n">
-        <v>10.03739060072383</v>
+        <v>10.03740042811715</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -3998,16 +3998,16 @@
         <v>116.4375</v>
       </c>
       <c r="M67" t="n">
-        <v>-42.13430248585986</v>
+        <v>-42.12291702338526</v>
       </c>
       <c r="N67" t="n">
-        <v>-5.5421496732783</v>
+        <v>-5.542104169367047</v>
       </c>
       <c r="O67" t="n">
-        <v>34.53141764013869</v>
+        <v>34.53145325599418</v>
       </c>
       <c r="P67" t="n">
-        <v>10.53321692502737</v>
+        <v>10.53322778903347</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -4051,16 +4051,16 @@
         <v>311.4</v>
       </c>
       <c r="M68" t="n">
-        <v>-23.40134070145032</v>
+        <v>-23.40002340134079</v>
       </c>
       <c r="N68" t="n">
-        <v>-3.760721102021232</v>
+        <v>-3.760701459055687</v>
       </c>
       <c r="O68" t="n">
-        <v>93.25024088034348</v>
+        <v>93.25033349715675</v>
       </c>
       <c r="P68" t="n">
-        <v>25.13079159830551</v>
+        <v>25.13081655838937</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -4104,16 +4104,16 @@
         <v>307.8</v>
       </c>
       <c r="M69" t="n">
-        <v>-21.06279147735271</v>
+        <v>-21.06012373089485</v>
       </c>
       <c r="N69" t="n">
-        <v>-2.741557652442058</v>
+        <v>-2.741543417419673</v>
       </c>
       <c r="O69" t="n">
-        <v>104.8506772597144</v>
+        <v>104.8507927005917</v>
       </c>
       <c r="P69" t="n">
-        <v>31.85347250951934</v>
+        <v>31.85350758027815</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -4157,16 +4157,16 @@
         <v>307.8</v>
       </c>
       <c r="M70" t="n">
-        <v>25.26946484164111</v>
+        <v>25.27202526946452</v>
       </c>
       <c r="N70" t="n">
-        <v>-1.939752966301787</v>
+        <v>-1.939741768039627</v>
       </c>
       <c r="O70" t="n">
-        <v>109.5284033053495</v>
+        <v>109.5285290229143</v>
       </c>
       <c r="P70" t="n">
-        <v>33.95750861754905</v>
+        <v>33.95754759424516</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -4210,16 +4210,16 @@
         <v>702</v>
       </c>
       <c r="M71" t="n">
-        <v>-3.159080927735068</v>
+        <v>-3.159006239111871</v>
       </c>
       <c r="N71" t="n">
-        <v>-3.929135280273193</v>
+        <v>-3.929111265615462</v>
       </c>
       <c r="O71" t="n">
-        <v>224.5701233871141</v>
+        <v>224.570351437623</v>
       </c>
       <c r="P71" t="n">
-        <v>61.15909083820386</v>
+        <v>61.15915294513766</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -4263,16 +4263,16 @@
         <v>705.857142857143</v>
       </c>
       <c r="M72" t="n">
-        <v>-6.793685509911766</v>
+        <v>-6.793478261076847</v>
       </c>
       <c r="N72" t="n">
-        <v>-5.185991825621334</v>
+        <v>-5.18596631607334</v>
       </c>
       <c r="O72" t="n">
-        <v>226.3320917156156</v>
+        <v>226.332324441161</v>
       </c>
       <c r="P72" t="n">
-        <v>68.13465564730738</v>
+        <v>68.13472570663824</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -4316,16 +4316,16 @@
         <v>711.642857142857</v>
       </c>
       <c r="M73" t="n">
-        <v>-16.43768765950295</v>
+        <v>-16.43730850525953</v>
       </c>
       <c r="N73" t="n">
-        <v>-2.981958804101001</v>
+        <v>-2.981944395724806</v>
       </c>
       <c r="O73" t="n">
-        <v>217.5308556243278</v>
+        <v>217.5310704013455</v>
       </c>
       <c r="P73" t="n">
-        <v>64.52481641520332</v>
+        <v>64.52488012316603</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -4369,16 +4369,16 @@
         <v>257.4</v>
       </c>
       <c r="M74" t="n">
-        <v>13.92556768948211</v>
+        <v>13.92558411562839</v>
       </c>
       <c r="N74" t="n">
-        <v>2.717275076297515</v>
+        <v>2.717428909515504</v>
       </c>
       <c r="O74" t="n">
-        <v>21.73820061038019</v>
+        <v>21.7394312761241</v>
       </c>
       <c r="P74" t="n">
-        <v>49.0996510314321</v>
+        <v>49.10243071221825</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
@@ -4422,16 +4422,16 @@
         <v>261</v>
       </c>
       <c r="M75" t="n">
-        <v>13.26685361393019</v>
+        <v>13.26686841857603</v>
       </c>
       <c r="N75" t="n">
-        <v>-12.03580652441012</v>
+        <v>-12.03429775009205</v>
       </c>
       <c r="O75" t="n">
-        <v>-96.28645219528096</v>
+        <v>-96.27438200073641</v>
       </c>
       <c r="P75" t="n">
-        <v>-119.1043353978082</v>
+        <v>-119.089404818619</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
@@ -4475,16 +4475,16 @@
         <v>261</v>
       </c>
       <c r="M76" t="n">
-        <v>13.81686947444445</v>
+        <v>13.81688536538721</v>
       </c>
       <c r="N76" t="n">
-        <v>-25.28089887640474</v>
+        <v>-25.27202528089601</v>
       </c>
       <c r="O76" t="n">
-        <v>-5.701303263289074e-13</v>
+        <v>-5.700588564201337e-13</v>
       </c>
       <c r="P76" t="n">
-        <v>-85.00288357864629</v>
+        <v>-84.99222786002493</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
@@ -4528,16 +4528,16 @@
         <v>149.4</v>
       </c>
       <c r="M77" t="n">
-        <v>-21.06179946700476</v>
+        <v>-21.0600210617993</v>
       </c>
       <c r="N77" t="n">
-        <v>12.90350185974732</v>
+        <v>12.90351596038889</v>
       </c>
       <c r="O77" t="n">
-        <v>404.4786018023767</v>
+        <v>404.3366353497914</v>
       </c>
       <c r="P77" t="n">
-        <v>273.163502516296</v>
+        <v>273.0676258660723</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
@@ -4581,16 +4581,16 @@
         <v>154.8</v>
       </c>
       <c r="M78" t="n">
-        <v>-36.10811989990074</v>
+        <v>-36.10289325097627</v>
       </c>
       <c r="N78" t="n">
-        <v>16.22165841926515</v>
+        <v>16.22167958579363</v>
       </c>
       <c r="O78" t="n">
-        <v>-48.13622551821653</v>
+        <v>-48.13743236820778</v>
       </c>
       <c r="P78" t="n">
-        <v>-18.1847964740215</v>
+        <v>-18.18525239513349</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
@@ -4634,16 +4634,16 @@
         <v>147.6</v>
       </c>
       <c r="M79" t="n">
-        <v>-12.03603996663357</v>
+        <v>-12.03429775032542</v>
       </c>
       <c r="N79" t="n">
-        <v>13.79075720805782</v>
+        <v>13.79077312045856</v>
       </c>
       <c r="O79" t="n">
-        <v>-33.69496051046803</v>
+        <v>-33.69594608550043</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.03899899188109859</v>
+        <v>-0.03900013259864522</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
@@ -4687,16 +4687,16 @@
         <v>447.1875</v>
       </c>
       <c r="M80" t="n">
-        <v>19.74744645276867</v>
+        <v>19.74747668366201</v>
       </c>
       <c r="N80" t="n">
-        <v>18.92105502096551</v>
+        <v>18.92108269296464</v>
       </c>
       <c r="O80" t="n">
-        <v>-17.08109837357535</v>
+        <v>-17.08095101947792</v>
       </c>
       <c r="P80" t="n">
-        <v>-8.163125927270542</v>
+        <v>-8.163055506152009</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -4740,16 +4740,16 @@
         <v>448.875</v>
       </c>
       <c r="M81" t="n">
-        <v>22.47293811817789</v>
+        <v>22.47297691806081</v>
       </c>
       <c r="N81" t="n">
-        <v>19.83757404164959</v>
+        <v>19.83760483426002</v>
       </c>
       <c r="O81" t="n">
-        <v>-33.18592895339346</v>
+        <v>-33.185458317</v>
       </c>
       <c r="P81" t="n">
-        <v>-19.0570906115908</v>
+        <v>-19.05682034763622</v>
       </c>
       <c r="Q81" t="n">
         <v>1</v>
@@ -4793,16 +4793,16 @@
         <v>453.9375</v>
       </c>
       <c r="M82" t="n">
-        <v>22.42836119878349</v>
+        <v>22.42839961485667</v>
       </c>
       <c r="N82" t="n">
-        <v>22.8393879933375</v>
+        <v>22.83942769181764</v>
       </c>
       <c r="O82" t="n">
-        <v>-28.08043460854473</v>
+        <v>-28.08003637680898</v>
       </c>
       <c r="P82" t="n">
-        <v>-18.00232408142498</v>
+        <v>-18.00206877566258</v>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
@@ -4846,16 +4846,16 @@
         <v>156.6</v>
       </c>
       <c r="M83" t="n">
-        <v>0.6194024795919707</v>
+        <v>0.6194117091317736</v>
       </c>
       <c r="N83" t="n">
-        <v>-2.025031717059271</v>
+        <v>-2.024997544724651</v>
       </c>
       <c r="O83" t="n">
-        <v>129.2515431204524</v>
+        <v>129.2518816821509</v>
       </c>
       <c r="P83" t="n">
-        <v>43.68805536353606</v>
+        <v>43.68816980009807</v>
       </c>
       <c r="Q83" t="n">
         <v>1</v>
@@ -4902,13 +4902,13 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>9.685605365938671e-15</v>
+        <v>9.685440334944847e-15</v>
       </c>
       <c r="O84" t="n">
-        <v>139.4314374074515</v>
+        <v>139.4318209530594</v>
       </c>
       <c r="P84" t="n">
-        <v>52.88645864101292</v>
+        <v>52.88660412017678</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
@@ -4952,16 +4952,16 @@
         <v>167.4</v>
       </c>
       <c r="M85" t="n">
-        <v>-3.85608135502731</v>
+        <v>-3.856053839767281</v>
       </c>
       <c r="N85" t="n">
-        <v>16.38168458323174</v>
+        <v>16.38008736206342</v>
       </c>
       <c r="O85" t="n">
-        <v>147.700438872427</v>
+        <v>147.7008708959861</v>
       </c>
       <c r="P85" t="n">
-        <v>52.15262248683804</v>
+        <v>52.15277503317949</v>
       </c>
       <c r="Q85" t="n">
         <v>1</v>
@@ -5005,16 +5005,16 @@
         <v>343.8</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2735042748367553</v>
+        <v>-0.2735060743655133</v>
       </c>
       <c r="N86" t="n">
-        <v>-19.74509328337743</v>
+        <v>-19.74401037521965</v>
       </c>
       <c r="O86" t="n">
-        <v>256.4508737708354</v>
+        <v>256.4514778928576</v>
       </c>
       <c r="P86" t="n">
-        <v>83.45772299339687</v>
+        <v>83.45791959498233</v>
       </c>
       <c r="Q86" t="n">
         <v>1</v>
@@ -5058,16 +5058,16 @@
         <v>347.4</v>
       </c>
       <c r="M87" t="n">
-        <v>-2.45701857198344</v>
+        <v>-2.456997825577663</v>
       </c>
       <c r="N87" t="n">
-        <v>1.914707578058188</v>
+        <v>1.91455483601705</v>
       </c>
       <c r="O87" t="n">
-        <v>315.3450287038027</v>
+        <v>315.3459389508985</v>
       </c>
       <c r="P87" t="n">
-        <v>106.9065677458002</v>
+        <v>106.9068763328524</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
@@ -5111,16 +5111,16 @@
         <v>349.2</v>
       </c>
       <c r="M88" t="n">
-        <v>0.4786309281853916</v>
+        <v>0.4786364392336501</v>
       </c>
       <c r="N88" t="n">
-        <v>-4.212051092179706</v>
+        <v>-4.211994229624725</v>
       </c>
       <c r="O88" t="n">
-        <v>303.1576519735167</v>
+        <v>303.1584858941292</v>
       </c>
       <c r="P88" t="n">
-        <v>110.6124183004658</v>
+        <v>110.6127225711151</v>
       </c>
       <c r="Q88" t="n">
         <v>1</v>
@@ -5164,16 +5164,16 @@
         <v>766.8</v>
       </c>
       <c r="M89" t="n">
-        <v>49.91680838685947</v>
+        <v>49.92290852189137</v>
       </c>
       <c r="N89" t="n">
-        <v>7.017698896530092</v>
+        <v>7.019751498741932</v>
       </c>
       <c r="O89" t="n">
-        <v>613.8176642741278</v>
+        <v>613.8192392002034</v>
       </c>
       <c r="P89" t="n">
-        <v>208.0679861175341</v>
+        <v>208.0685199759027</v>
       </c>
       <c r="Q89" t="n">
         <v>1</v>
@@ -5217,16 +5217,16 @@
         <v>756</v>
       </c>
       <c r="M90" t="n">
-        <v>-3.569546959261185</v>
+        <v>-3.569485657008598</v>
       </c>
       <c r="N90" t="n">
-        <v>91.12949333811125</v>
+        <v>91.13006699585912</v>
       </c>
       <c r="O90" t="n">
-        <v>611.7180244381105</v>
+        <v>611.719584851115</v>
       </c>
       <c r="P90" t="n">
-        <v>209.8070110172233</v>
+        <v>209.8075462075811</v>
       </c>
       <c r="Q90" t="n">
         <v>1</v>
@@ -5270,16 +5270,16 @@
         <v>747</v>
       </c>
       <c r="M91" t="n">
-        <v>-9.36014831373741</v>
+        <v>-9.359997771579655</v>
       </c>
       <c r="N91" t="n">
-        <v>8.552941418103881e-13</v>
+        <v>8.550797095009467e-13</v>
       </c>
       <c r="O91" t="n">
-        <v>623.0181847603666</v>
+        <v>623.0198364160523</v>
       </c>
       <c r="P91" t="n">
-        <v>218.8159791354512</v>
+        <v>218.8165592287213</v>
       </c>
       <c r="Q91" t="n">
         <v>1</v>
@@ -5323,16 +5323,16 @@
         <v>258.882352941176</v>
       </c>
       <c r="M92" t="n">
-        <v>9.331455870128789</v>
+        <v>9.331463130131072</v>
       </c>
       <c r="N92" t="n">
-        <v>7.021558786053578</v>
+        <v>7.019231396492033</v>
       </c>
       <c r="O92" t="n">
-        <v>56.17247028842862</v>
+        <v>56.15385117193626</v>
       </c>
       <c r="P92" t="n">
-        <v>-193.8135830344189</v>
+        <v>-146.2956394956674</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -5376,16 +5376,16 @@
         <v>266.823529411765</v>
       </c>
       <c r="M93" t="n">
-        <v>11.03220168268138</v>
+        <v>11.03221158792877</v>
       </c>
       <c r="N93" t="n">
-        <v>1.180953322382473</v>
+        <v>1.180931369976626</v>
       </c>
       <c r="O93" t="n">
-        <v>-12.17952449952328</v>
+        <v>-12.17923263251677</v>
       </c>
       <c r="P93" t="n">
-        <v>-10.96721071832</v>
+        <v>-10.96694790289053</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -5429,7 +5429,7 @@
         <v>214.411764705882</v>
       </c>
       <c r="M94" t="n">
-        <v>10.81024909913242</v>
+        <v>10.81026089944393</v>
       </c>
       <c r="N94" t="n">
         <v>-0</v>
@@ -5438,7 +5438,7 @@
         <v>-0</v>
       </c>
       <c r="P94" t="n">
-        <v>-160.8964609062774</v>
+        <v>-146.2956394956674</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -5482,16 +5482,16 @@
         <v>152.470588235294</v>
       </c>
       <c r="M95" t="n">
-        <v>-12.03205574517937</v>
+        <v>-12.03402955939541</v>
       </c>
       <c r="N95" t="n">
-        <v>11.45694432657463</v>
+        <v>11.45695494038067</v>
       </c>
       <c r="O95" t="n">
-        <v>48.15221450028788</v>
+        <v>48.1385320113227</v>
       </c>
       <c r="P95" t="n">
-        <v>344.0153310954266</v>
+        <v>404.2683458094837</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -5535,16 +5535,16 @@
         <v>152.470588235294</v>
       </c>
       <c r="M96" t="n">
-        <v>-0.7020109437620721</v>
+        <v>-0.7019975079224311</v>
       </c>
       <c r="N96" t="n">
-        <v>12.09567338816548</v>
+        <v>12.09568507828705</v>
       </c>
       <c r="O96" t="n">
-        <v>-474.0710372077395</v>
+        <v>991.7021157320429</v>
       </c>
       <c r="P96" t="n">
-        <v>-193.8135830344189</v>
+        <v>404.2683458094837</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -5588,16 +5588,16 @@
         <v>144.529411764706</v>
       </c>
       <c r="M97" t="n">
-        <v>21.05570376021407</v>
+        <v>21.05973359033761</v>
       </c>
       <c r="N97" t="n">
-        <v>11.13257324715435</v>
+        <v>11.13258398559016</v>
       </c>
       <c r="O97" t="n">
-        <v>-33.69448635943254</v>
+        <v>-33.69616182413764</v>
       </c>
       <c r="P97" t="n">
-        <v>-57.29817602268641</v>
+        <v>-57.30102518532295</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -5641,16 +5641,16 @@
         <v>455.823529411765</v>
       </c>
       <c r="M98" t="n">
-        <v>17.719087749147</v>
+        <v>17.71911165948063</v>
       </c>
       <c r="N98" t="n">
-        <v>18.77958633572569</v>
+        <v>18.77961277065123</v>
       </c>
       <c r="O98" t="n">
-        <v>-45.95038587451175</v>
+        <v>-45.94900110106514</v>
       </c>
       <c r="P98" t="n">
-        <v>93.77991561580372</v>
+        <v>93.77708943851492</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -5694,16 +5694,16 @@
         <v>427.235294117647</v>
       </c>
       <c r="M99" t="n">
-        <v>17.71795417813971</v>
+        <v>17.7179798033046</v>
       </c>
       <c r="N99" t="n">
-        <v>19.07439698377148</v>
+        <v>19.074426302874</v>
       </c>
       <c r="O99" t="n">
-        <v>-31.28966052222591</v>
+        <v>-31.28921598495451</v>
       </c>
       <c r="P99" t="n">
-        <v>29.45105867530091</v>
+        <v>29.45064025934353</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -5747,16 +5747,16 @@
         <v>168.230769230769</v>
       </c>
       <c r="M100" t="n">
-        <v>-0.8961856223870951</v>
+        <v>-0.8961688780630602</v>
       </c>
       <c r="N100" t="n">
-        <v>-3.654264546314717</v>
+        <v>-3.6542391667734</v>
       </c>
       <c r="O100" t="n">
-        <v>125.8849321737525</v>
+        <v>125.8852405003636</v>
       </c>
       <c r="P100" t="n">
-        <v>44.23381282290719</v>
+        <v>44.23392116360667</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -5800,16 +5800,16 @@
         <v>168.230769230769</v>
       </c>
       <c r="M101" t="n">
-        <v>-2.372985558864158</v>
+        <v>-2.372956209099879</v>
       </c>
       <c r="N101" t="n">
-        <v>-2.674218858814172</v>
+        <v>-2.674283421978145</v>
       </c>
       <c r="O101" t="n">
-        <v>165.7062738814247</v>
+        <v>165.7067924805644</v>
       </c>
       <c r="P101" t="n">
-        <v>48.46821844570449</v>
+        <v>48.46837013324051</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -5853,16 +5853,16 @@
         <v>153.692307692308</v>
       </c>
       <c r="M102" t="n">
-        <v>7.019493338960904</v>
+        <v>7.020007019493114</v>
       </c>
       <c r="N102" t="n">
-        <v>-0.3829113065731317</v>
+        <v>-0.3829086592692301</v>
       </c>
       <c r="O102" t="n">
-        <v>150.5268223002384</v>
+        <v>150.5272914625067</v>
       </c>
       <c r="P102" t="n">
-        <v>50.58558587717765</v>
+        <v>50.58574354242197</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -5906,16 +5906,16 @@
         <v>354.6</v>
       </c>
       <c r="M103" t="n">
-        <v>-7.433357553686427</v>
+        <v>-7.432914505867563</v>
       </c>
       <c r="N103" t="n">
-        <v>-4.481022868153396</v>
+        <v>-4.480855544852674</v>
       </c>
       <c r="O103" t="n">
-        <v>284.7818673706747</v>
+        <v>284.7825906586746</v>
       </c>
       <c r="P103" t="n">
-        <v>92.74814705196113</v>
+        <v>92.74838261338364</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -5959,16 +5959,16 @@
         <v>352.8</v>
       </c>
       <c r="M104" t="n">
-        <v>-3.240247043843002</v>
+        <v>-3.239994492261967</v>
       </c>
       <c r="N104" t="n">
-        <v>-0.3727488943594445</v>
+        <v>-0.3727431052160525</v>
       </c>
       <c r="O104" t="n">
-        <v>300.0883703777934</v>
+        <v>300.0891707651314</v>
       </c>
       <c r="P104" t="n">
-        <v>96.78795900155504</v>
+        <v>96.7882171517018</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -6012,16 +6012,16 @@
         <v>327.6</v>
       </c>
       <c r="M105" t="n">
-        <v>-1.531621669122699</v>
+        <v>-1.531635777423474</v>
       </c>
       <c r="N105" t="n">
-        <v>-1.337159549351203</v>
+        <v>-1.33714092467445</v>
       </c>
       <c r="O105" t="n">
-        <v>278.2696017964928</v>
+        <v>278.270335073935</v>
       </c>
       <c r="P105" t="n">
-        <v>91.96950879577004</v>
+        <v>91.96975114766812</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -6065,16 +6065,16 @@
         <v>762.75</v>
       </c>
       <c r="M106" t="n">
-        <v>-11.79406463883085</v>
+        <v>-11.79355476043381</v>
       </c>
       <c r="N106" t="n">
-        <v>-2.477928653550422</v>
+        <v>-2.477655789188902</v>
       </c>
       <c r="O106" t="n">
-        <v>584.7874318971462</v>
+        <v>584.7888444408247</v>
       </c>
       <c r="P106" t="n">
-        <v>182.6615307077739</v>
+        <v>182.6619719234644</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -6118,16 +6118,16 @@
         <v>757.6875</v>
       </c>
       <c r="M107" t="n">
-        <v>-6.164059366910741</v>
+        <v>-6.163896876645749</v>
       </c>
       <c r="N107" t="n">
-        <v>-2.61617449883902</v>
+        <v>-2.61614407980532</v>
       </c>
       <c r="O107" t="n">
-        <v>557.9710471418854</v>
+        <v>557.9723446833628</v>
       </c>
       <c r="P107" t="n">
-        <v>172.7512104386444</v>
+        <v>172.7516121653325</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -6171,16 +6171,16 @@
         <v>384.75</v>
       </c>
       <c r="M108" t="n">
-        <v>24.06501393295822</v>
+        <v>24.06872959079257</v>
       </c>
       <c r="N108" t="n">
-        <v>-2.092942843814162</v>
+        <v>-2.092918508511747</v>
       </c>
       <c r="O108" t="n">
-        <v>487.3609785811021</v>
+        <v>487.3629363905324</v>
       </c>
       <c r="P108" t="n">
-        <v>168.0701412957341</v>
+        <v>168.0708164612112</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -6224,16 +6224,16 @@
         <v>298.8</v>
       </c>
       <c r="M109" t="n">
-        <v>27.74164066412741</v>
+        <v>27.74169710828824</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.831336455931553</v>
+        <v>-1.831301521286928</v>
       </c>
       <c r="O109" t="n">
-        <v>-14.65069164745242</v>
+        <v>-14.65041217029542</v>
       </c>
       <c r="P109" t="n">
-        <v>-11.59846422089988</v>
+        <v>-11.59824296815058</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -6277,16 +6277,16 @@
         <v>300.6</v>
       </c>
       <c r="M110" t="n">
-        <v>31.02583723573091</v>
+        <v>31.02590740739224</v>
       </c>
       <c r="N110" t="n">
-        <v>-4.433782611330689</v>
+        <v>-4.433680226150309</v>
       </c>
       <c r="O110" t="n">
-        <v>-7.405851822962531</v>
+        <v>-7.405708996065075</v>
       </c>
       <c r="P110" t="n">
-        <v>-3.330061844005681</v>
+        <v>-3.329997621494498</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>306</v>
       </c>
       <c r="M111" t="n">
-        <v>36.58354193977905</v>
+        <v>36.58363747652199</v>
       </c>
       <c r="N111" t="n">
-        <v>-4.212743549236305</v>
+        <v>-4.212004212743285</v>
       </c>
       <c r="O111" t="n">
-        <v>168.4432162126593</v>
+        <v>168.4801684432078</v>
       </c>
       <c r="P111" t="n">
-        <v>26.17303300141845</v>
+        <v>26.17877471053187</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -6383,16 +6383,16 @@
         <v>175.5</v>
       </c>
       <c r="M112" t="n">
-        <v>-2.47770223383712</v>
+        <v>-2.477649725993089</v>
       </c>
       <c r="N112" t="n">
-        <v>39.09785255447086</v>
+        <v>39.09796195828716</v>
       </c>
       <c r="O112" t="n">
-        <v>-22.46314056024216</v>
+        <v>-22.46407502907609</v>
       </c>
       <c r="P112" t="n">
-        <v>20.85120249299262</v>
+        <v>20.85206990504604</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -6436,16 +6436,16 @@
         <v>180.5625</v>
       </c>
       <c r="M113" t="n">
-        <v>6.016963740778864</v>
+        <v>6.017149544588978</v>
       </c>
       <c r="N113" t="n">
-        <v>38.55355483947405</v>
+        <v>38.55366020039316</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-1.903384771094117</v>
+        <v>-1.903437952322567</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
@@ -6489,16 +6489,16 @@
         <v>87.75</v>
       </c>
       <c r="M114" t="n">
-        <v>8.424879557176325</v>
+        <v>8.423969000704538</v>
       </c>
       <c r="N114" t="n">
-        <v>29.63299606846831</v>
+        <v>29.63311879624115</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>43.28650546159385</v>
+        <v>43.29002860553893</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -6542,16 +6542,16 @@
         <v>502.2</v>
       </c>
       <c r="M115" t="n">
-        <v>49.91680838685947</v>
+        <v>49.92290852189137</v>
       </c>
       <c r="N115" t="n">
-        <v>75.02977859461392</v>
+        <v>75.0301624933353</v>
       </c>
       <c r="O115" t="n">
-        <v>-46.7081796425317</v>
+        <v>-46.70736803019725</v>
       </c>
       <c r="P115" t="n">
-        <v>-20.77077520634375</v>
+        <v>-20.77041428845994</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -6595,16 +6595,16 @@
         <v>489.6</v>
       </c>
       <c r="M116" t="n">
-        <v>46.40094083797657</v>
+        <v>46.4010949879432</v>
       </c>
       <c r="N116" t="n">
-        <v>62.09314794350809</v>
+        <v>62.09341569154915</v>
       </c>
       <c r="O116" t="n">
-        <v>-31.10443981677895</v>
+        <v>-31.10401990699259</v>
       </c>
       <c r="P116" t="n">
-        <v>-16.58723455249653</v>
+        <v>-16.58701062491068</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -6648,16 +6648,16 @@
         <v>496.8</v>
       </c>
       <c r="M117" t="n">
-        <v>44.76065438984813</v>
+        <v>44.76079656451924</v>
       </c>
       <c r="N117" t="n">
-        <v>85.79955063568677</v>
+        <v>85.80005763286499</v>
       </c>
       <c r="O117" t="n">
-        <v>-33.49931627229526</v>
+        <v>-33.49897246360924</v>
       </c>
       <c r="P117" t="n">
-        <v>-19.52074128367202</v>
+        <v>-19.52054093927227</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -6701,16 +6701,16 @@
         <v>171</v>
       </c>
       <c r="M118" t="n">
-        <v>15.04396099319675</v>
+        <v>15.04287218681806</v>
       </c>
       <c r="N118" t="n">
-        <v>-1.070863889035218</v>
+        <v>-1.07084796221207</v>
       </c>
       <c r="O118" t="n">
-        <v>290.103332235261</v>
+        <v>290.1048385406768</v>
       </c>
       <c r="P118" t="n">
-        <v>114.0052649767127</v>
+        <v>114.0058569269903</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -6754,16 +6754,16 @@
         <v>176.4</v>
       </c>
       <c r="M119" t="n">
-        <v>-4.755566943797704</v>
+        <v>-4.755489224805896</v>
       </c>
       <c r="N119" t="n">
-        <v>-52.67326578149263</v>
+        <v>-52.65015534105545</v>
       </c>
       <c r="O119" t="n">
-        <v>208.0999732897912</v>
+        <v>208.100775961103</v>
       </c>
       <c r="P119" t="n">
-        <v>71.80693646349135</v>
+        <v>71.80721343309868</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -6807,16 +6807,16 @@
         <v>187.2</v>
       </c>
       <c r="M120" t="n">
-        <v>-5.214913262759926</v>
+        <v>-5.214862938855118</v>
       </c>
       <c r="N120" t="n">
-        <v>-3.973721924090861</v>
+        <v>-3.973590341363636</v>
       </c>
       <c r="O120" t="n">
-        <v>284.8921054721603</v>
+        <v>284.8935631561739</v>
       </c>
       <c r="P120" t="n">
-        <v>108.0147678625651</v>
+        <v>108.0153205328474</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -6860,16 +6860,16 @@
         <v>367.2</v>
       </c>
       <c r="M121" t="n">
-        <v>-2.029906614873141</v>
+        <v>-2.029881834118876</v>
       </c>
       <c r="N121" t="n">
-        <v>-22.46641154461441</v>
+        <v>-22.46378300248367</v>
       </c>
       <c r="O121" t="n">
-        <v>466.3201356119717</v>
+        <v>466.3220169720971</v>
       </c>
       <c r="P121" t="n">
-        <v>156.8063855791919</v>
+        <v>156.8070182117092</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -6916,13 +6916,13 @@
         <v>-0</v>
       </c>
       <c r="N122" t="n">
-        <v>-1.65170724590213</v>
+        <v>-1.651764083985001</v>
       </c>
       <c r="O122" t="n">
-        <v>473.0079978845592</v>
+        <v>473.0099465438406</v>
       </c>
       <c r="P122" t="n">
-        <v>166.1888816424812</v>
+        <v>166.1895662937094</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -6966,16 +6966,16 @@
         <v>334.8</v>
       </c>
       <c r="M123" t="n">
-        <v>-2.105895005368965</v>
+        <v>-2.106001695224637</v>
       </c>
       <c r="N123" t="n">
-        <v>-2.632213269718406</v>
+        <v>-2.63250199054102</v>
       </c>
       <c r="O123" t="n">
-        <v>536.070584665609</v>
+        <v>536.0732574038636</v>
       </c>
       <c r="P123" t="n">
-        <v>202.8778538953047</v>
+        <v>202.8788654027753</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -7019,16 +7019,16 @@
         <v>778.95</v>
       </c>
       <c r="M124" t="n">
-        <v>6.142371490106965</v>
+        <v>6.142501151589267</v>
       </c>
       <c r="N124" t="n">
-        <v>39.77624777396029</v>
+        <v>39.78012596652063</v>
       </c>
       <c r="O124" t="n">
-        <v>934.1794794818037</v>
+        <v>969.4201184562716</v>
       </c>
       <c r="P124" t="n">
-        <v>333.3729642952375</v>
+        <v>333.3742731750625</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -7072,16 +7072,16 @@
         <v>774</v>
       </c>
       <c r="M125" t="n">
-        <v>-3.008801419142975</v>
+        <v>-3.008583656532615</v>
       </c>
       <c r="N125" t="n">
-        <v>-4.860111539559767</v>
+        <v>-4.860002187110268</v>
       </c>
       <c r="O125" t="n">
-        <v>858.4430188768313</v>
+        <v>858.4460080960916</v>
       </c>
       <c r="P125" t="n">
-        <v>301.5688745382068</v>
+        <v>301.5699246434185</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -7125,16 +7125,16 @@
         <v>765</v>
       </c>
       <c r="M126" t="n">
-        <v>6.793431764722391</v>
+        <v>6.793542787791635</v>
       </c>
       <c r="N126" t="n">
-        <v>-4.43348798201492</v>
+        <v>-4.43369273934637</v>
       </c>
       <c r="O126" t="n">
-        <v>922.4338685222618</v>
+        <v>922.4373801713892</v>
       </c>
       <c r="P126" t="n">
-        <v>332.8270203766328</v>
+        <v>332.8282874286737</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -7178,16 +7178,16 @@
         <v>278.307692307692</v>
       </c>
       <c r="M127" t="n">
-        <v>21.9829095334636</v>
+        <v>21.98294798817918</v>
       </c>
       <c r="N127" t="n">
-        <v>-118.5271903786999</v>
+        <v>-118.4650132973987</v>
       </c>
       <c r="O127" t="n">
-        <v>-474.0710372077395</v>
+        <v>-174.7991655562957</v>
       </c>
       <c r="P127" t="n">
-        <v>132.3133367159499</v>
+        <v>132.212710461087</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
@@ -7231,16 +7231,16 @@
         <v>270</v>
       </c>
       <c r="M128" t="n">
-        <v>18.55283322138428</v>
+        <v>18.55286092912759</v>
       </c>
       <c r="N128" t="n">
-        <v>3.760625857283397</v>
+        <v>3.760727998838151</v>
       </c>
       <c r="O128" t="n">
-        <v>337.4195992360779</v>
+        <v>336.9064660749339</v>
       </c>
       <c r="P128" t="n">
-        <v>231.9759744747932</v>
+        <v>231.6231954265068</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
@@ -7284,16 +7284,16 @@
         <v>176.538461538462</v>
       </c>
       <c r="M129" t="n">
-        <v>19.69550058132522</v>
+        <v>19.69554930127397</v>
       </c>
       <c r="N129" t="n">
-        <v>-4.757585024527412e-12</v>
+        <v>-4.755172963411261e-12</v>
       </c>
       <c r="O129" t="n">
-        <v>168.4592542428501</v>
+        <v>168.4806065088385</v>
       </c>
       <c r="P129" t="n">
-        <v>-29.05142329222167</v>
+        <v>-29.05510556969742</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
@@ -7337,16 +7337,16 @@
         <v>160.5</v>
       </c>
       <c r="M130" t="n">
-        <v>-1.560069561749115</v>
+        <v>-1.559999306737239</v>
       </c>
       <c r="N130" t="n">
-        <v>21.24396585253974</v>
+        <v>21.24400138847586</v>
       </c>
       <c r="O130" t="n">
-        <v>9.106839352297111</v>
+        <v>9.107098529798174</v>
       </c>
       <c r="P130" t="n">
-        <v>-2.60873018089829</v>
+        <v>-2.608804424457781</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
@@ -7390,16 +7390,16 @@
         <v>482.4</v>
       </c>
       <c r="M131" t="n">
-        <v>30.12489219528911</v>
+        <v>30.124958551833</v>
       </c>
       <c r="N131" t="n">
-        <v>33.19421565458482</v>
+        <v>33.19429634128146</v>
       </c>
       <c r="O131" t="n">
-        <v>-47.61437443711744</v>
+        <v>-47.61392028952891</v>
       </c>
       <c r="P131" t="n">
-        <v>-16.85706552254249</v>
+        <v>-16.85690473925493</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
@@ -7443,16 +7443,16 @@
         <v>466.2</v>
       </c>
       <c r="M132" t="n">
-        <v>46.38693801288444</v>
+        <v>46.38709161268276</v>
       </c>
       <c r="N132" t="n">
-        <v>21.55067904233609</v>
+        <v>21.55071576214113</v>
       </c>
       <c r="O132" t="n">
-        <v>-11.87532088235492</v>
+        <v>-11.8752290711474</v>
       </c>
       <c r="P132" t="n">
-        <v>-4.736727331654054</v>
+        <v>-4.736690710777842</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
@@ -7496,16 +7496,16 @@
         <v>455.4</v>
       </c>
       <c r="M133" t="n">
-        <v>24.82353274441594</v>
+        <v>24.82358056270304</v>
       </c>
       <c r="N133" t="n">
-        <v>38.13378455112986</v>
+        <v>38.13389011066059</v>
       </c>
       <c r="O133" t="n">
-        <v>-57.53244047704057</v>
+        <v>-57.52997780091434</v>
       </c>
       <c r="P133" t="n">
-        <v>-75.22594895708286</v>
+        <v>-75.22272891032259</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
@@ -7549,16 +7549,16 @@
         <v>160.3125</v>
       </c>
       <c r="M134" t="n">
-        <v>-3.576193790770405</v>
+        <v>-3.576230254444694</v>
       </c>
       <c r="N134" t="n">
-        <v>15.04085262694052</v>
+        <v>15.04286380268528</v>
       </c>
       <c r="O134" t="n">
-        <v>206.9291924364623</v>
+        <v>206.9299961116531</v>
       </c>
       <c r="P134" t="n">
-        <v>69.00309864620066</v>
+        <v>69.00336664163338</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
@@ -7602,16 +7602,16 @@
         <v>156.9375</v>
       </c>
       <c r="M135" t="n">
-        <v>-1.847351679837949</v>
+        <v>-1.847369194013277</v>
       </c>
       <c r="N135" t="n">
-        <v>-1.316332011597793</v>
+        <v>-1.316255005959254</v>
       </c>
       <c r="O135" t="n">
-        <v>195.4772269829549</v>
+        <v>195.4779692411746</v>
       </c>
       <c r="P135" t="n">
-        <v>75.48969397218352</v>
+        <v>75.48998061859609</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
@@ -7655,16 +7655,16 @@
         <v>167.0625</v>
       </c>
       <c r="M136" t="n">
-        <v>-5.542269576822753</v>
+        <v>-5.542111943018874</v>
       </c>
       <c r="N136" t="n">
-        <v>-6.81372458489329</v>
+        <v>-6.81353700704202</v>
       </c>
       <c r="O136" t="n">
-        <v>188.3787039017598</v>
+        <v>188.3793980846895</v>
       </c>
       <c r="P136" t="n">
-        <v>64.50183369367035</v>
+        <v>64.50207138546331</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
@@ -7708,16 +7708,16 @@
         <v>356.785714285714</v>
       </c>
       <c r="M137" t="n">
-        <v>-5.809756492537581</v>
+        <v>-5.809661763469497</v>
       </c>
       <c r="N137" t="n">
-        <v>-6.016444949529451</v>
+        <v>-6.017148873588464</v>
       </c>
       <c r="O137" t="n">
-        <v>387.5385594954874</v>
+        <v>387.5399015419731</v>
       </c>
       <c r="P137" t="n">
-        <v>135.4203272869399</v>
+        <v>135.420796247692</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
@@ -7761,16 +7761,16 @@
         <v>352.928571428571</v>
       </c>
       <c r="M138" t="n">
-        <v>5.376918909241269</v>
+        <v>5.377027099693212</v>
       </c>
       <c r="N138" t="n">
-        <v>1.379481181268838e-13</v>
+        <v>1.379397492997691e-13</v>
       </c>
       <c r="O138" t="n">
-        <v>427.1311322237809</v>
+        <v>427.1327745728835</v>
       </c>
       <c r="P138" t="n">
-        <v>158.9629809798113</v>
+        <v>158.9635922036006</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
@@ -7814,16 +7814,16 @@
         <v>337.5</v>
       </c>
       <c r="M139" t="n">
-        <v>-3.309450825115395</v>
+        <v>-3.309428469804237</v>
       </c>
       <c r="N139" t="n">
-        <v>-9.614506204175568</v>
+        <v>-9.614335024562038</v>
       </c>
       <c r="O139" t="n">
-        <v>336.2837121838404</v>
+        <v>336.2848160562082</v>
       </c>
       <c r="P139" t="n">
-        <v>120.7300355871969</v>
+        <v>120.7304318911076</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -7867,16 +7867,16 @@
         <v>745.875</v>
       </c>
       <c r="M140" t="n">
-        <v>-1.089299453713924</v>
+        <v>-1.089309602960027</v>
       </c>
       <c r="N140" t="n">
-        <v>-10.15412541640264</v>
+        <v>-10.15395569716557</v>
       </c>
       <c r="O140" t="n">
-        <v>729.8934929260779</v>
+        <v>729.8957402289487</v>
       </c>
       <c r="P140" t="n">
-        <v>252.3152762103515</v>
+        <v>252.3160530755381</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -7920,16 +7920,16 @@
         <v>749.25</v>
       </c>
       <c r="M141" t="n">
-        <v>-1.257333655259314</v>
+        <v>-1.257313372805306</v>
       </c>
       <c r="N141" t="n">
-        <v>-84.29421804103954</v>
+        <v>-84.24161749161816</v>
       </c>
       <c r="O141" t="n">
-        <v>813.8572136597394</v>
+        <v>813.8599887777233</v>
       </c>
       <c r="P141" t="n">
-        <v>280.905708826908</v>
+        <v>280.9066666687398</v>
       </c>
       <c r="Q141" t="n">
         <v>0</v>
@@ -7973,16 +7973,16 @@
         <v>231.882352941176</v>
       </c>
       <c r="M142" t="n">
-        <v>8.109873461494077</v>
+        <v>8.109879775362293</v>
       </c>
       <c r="N142" t="n">
-        <v>-2.572262260000305</v>
+        <v>-2.572223204707606</v>
       </c>
       <c r="O142" t="n">
-        <v>-20.57809808000251</v>
+        <v>-20.57778563766092</v>
       </c>
       <c r="P142" t="n">
-        <v>-12.35221772770997</v>
+        <v>-12.35203018093982</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -8026,16 +8026,16 @@
         <v>231.882352941176</v>
       </c>
       <c r="M143" t="n">
-        <v>8.279245052197185</v>
+        <v>8.279251586528376</v>
       </c>
       <c r="N143" t="n">
-        <v>-14.86787552283744</v>
+        <v>-14.8661359534656</v>
       </c>
       <c r="O143" t="n">
-        <v>-118.9430041826995</v>
+        <v>-118.9290876277248</v>
       </c>
       <c r="P143" t="n">
-        <v>-89.00075417755465</v>
+        <v>-88.99034092208989</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
@@ -8079,16 +8079,16 @@
         <v>7.94117647058824</v>
       </c>
       <c r="M144" t="n">
-        <v>1.893022019521036</v>
+        <v>1.893034232159625</v>
       </c>
       <c r="N144" t="n">
-        <v>-3.008782720337961</v>
+        <v>-3.008568989695282</v>
       </c>
       <c r="O144" t="n">
-        <v>-24.07026176270368</v>
+        <v>-24.06855191756225</v>
       </c>
       <c r="P144" t="n">
-        <v>-15.04391360168978</v>
+        <v>-15.04284494847639</v>
       </c>
       <c r="Q144" t="n">
         <v>0</v>
@@ -8132,16 +8132,16 @@
         <v>86.40000000000001</v>
       </c>
       <c r="M145" t="n">
-        <v>-5.850176845926114</v>
+        <v>-5.850012187690361</v>
       </c>
       <c r="N145" t="n">
-        <v>4.675557066328457</v>
+        <v>4.675559661393052</v>
       </c>
       <c r="O145" t="n">
-        <v>-25.46779000259253</v>
+        <v>-25.46787662250239</v>
       </c>
       <c r="P145" t="n">
-        <v>15.25301133791311</v>
+        <v>15.25306321577401</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
@@ -8185,16 +8185,16 @@
         <v>72</v>
       </c>
       <c r="M146" t="n">
-        <v>-42.14635812340187</v>
+        <v>-42.1271286654951</v>
       </c>
       <c r="N146" t="n">
-        <v>4.626069754053747</v>
+        <v>4.626072677621163</v>
       </c>
       <c r="O146" t="n">
-        <v>-27.53985197329539</v>
+        <v>-27.53996815679538</v>
       </c>
       <c r="P146" t="n">
-        <v>16.24491268359419</v>
+        <v>16.2449812166718</v>
       </c>
       <c r="Q146" t="n">
         <v>0</v>
@@ -8238,16 +8238,16 @@
         <v>5.95588235294118</v>
       </c>
       <c r="M147" t="n">
-        <v>5.74337453109583</v>
+        <v>5.743639052439206</v>
       </c>
       <c r="N147" t="n">
-        <v>3.204846270179985</v>
+        <v>3.20478513426681</v>
       </c>
       <c r="O147" t="n">
-        <v>-25.91654273319936</v>
+        <v>-25.92004146856711</v>
       </c>
       <c r="P147" t="n">
-        <v>74.60004835354957</v>
+        <v>74.61011936611855</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
@@ -8291,16 +8291,16 @@
         <v>416.117647058824</v>
       </c>
       <c r="M148" t="n">
-        <v>7.658175038460685</v>
+        <v>7.658180749014499</v>
       </c>
       <c r="N148" t="n">
-        <v>13.82823114555254</v>
+        <v>13.82824709932219</v>
       </c>
       <c r="O148" t="n">
-        <v>-31.99971441575725</v>
+        <v>-31.99964159266378</v>
       </c>
       <c r="P148" t="n">
-        <v>1.860759832576236</v>
+        <v>1.860755597966969</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
@@ -8344,16 +8344,16 @@
         <v>424.058823529412</v>
       </c>
       <c r="M149" t="n">
-        <v>7.667987454240178</v>
+        <v>7.667993098800594</v>
       </c>
       <c r="N149" t="n">
-        <v>14.62848448503731</v>
+        <v>14.6285019078064</v>
       </c>
       <c r="O149" t="n">
-        <v>-29.80398159928803</v>
+        <v>-29.80391991355244</v>
       </c>
       <c r="P149" t="n">
-        <v>1.279574536799498</v>
+        <v>1.279571888445409</v>
       </c>
       <c r="Q149" t="n">
         <v>0</v>
@@ -8397,16 +8397,16 @@
         <v>5.95588235294118</v>
       </c>
       <c r="M150" t="n">
-        <v>3.662656988966395</v>
+        <v>3.66261127146908</v>
       </c>
       <c r="N150" t="n">
-        <v>4.553639261646372</v>
+        <v>4.553516867239547</v>
       </c>
       <c r="O150" t="n">
-        <v>32.31037275688528</v>
+        <v>32.31125310356169</v>
       </c>
       <c r="P150" t="n">
-        <v>14.34413869911324</v>
+        <v>14.34452952762286</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
@@ -8453,13 +8453,13 @@
         <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>-1.643713338676662</v>
+        <v>-1.643698328864629</v>
       </c>
       <c r="O151" t="n">
-        <v>30.71200433131682</v>
+        <v>30.71203410490208</v>
       </c>
       <c r="P151" t="n">
-        <v>9.559329473153122</v>
+        <v>9.559338740392995</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
@@ -8503,16 +8503,16 @@
         <v>106.3125</v>
       </c>
       <c r="M152" t="n">
-        <v>-1.2763251570997</v>
+        <v>-1.276346057576577</v>
       </c>
       <c r="N152" t="n">
-        <v>-4.567271039108189</v>
+        <v>-4.567219533654743</v>
       </c>
       <c r="O152" t="n">
-        <v>32.38635990051157</v>
+        <v>32.38639174253615</v>
       </c>
       <c r="P152" t="n">
-        <v>9.388259080146019</v>
+        <v>9.38826831061148</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
@@ -8556,16 +8556,16 @@
         <v>32.0625</v>
       </c>
       <c r="M153" t="n">
-        <v>8.423296374142501</v>
+        <v>8.423903292983251</v>
       </c>
       <c r="N153" t="n">
-        <v>-1.159283142241248</v>
+        <v>-1.159263232419339</v>
       </c>
       <c r="O153" t="n">
-        <v>26.56089470287007</v>
+        <v>26.56097155281158</v>
       </c>
       <c r="P153" t="n">
-        <v>11.80122541060254</v>
+        <v>11.80125955566778</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
@@ -8609,16 +8609,16 @@
         <v>309.6</v>
       </c>
       <c r="M154" t="n">
-        <v>-7.897757972791525</v>
+        <v>-7.897507897757962</v>
       </c>
       <c r="N154" t="n">
-        <v>-3.617690939371057</v>
+        <v>-3.617671463769587</v>
       </c>
       <c r="O154" t="n">
-        <v>106.4196626136528</v>
+        <v>106.4197822589579</v>
       </c>
       <c r="P154" t="n">
-        <v>31.67840771048878</v>
+        <v>31.67844332583149</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
@@ -8665,13 +8665,13 @@
         <v>-0</v>
       </c>
       <c r="N155" t="n">
-        <v>-3.432026235933883</v>
+        <v>-3.432003927760127</v>
       </c>
       <c r="O155" t="n">
-        <v>102.2987843610444</v>
+        <v>102.2988955966119</v>
       </c>
       <c r="P155" t="n">
-        <v>30.83824111042513</v>
+        <v>30.83827464268334</v>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
@@ -8715,16 +8715,16 @@
         <v>280.8</v>
       </c>
       <c r="M156" t="n">
-        <v>-5.692029462047803</v>
+        <v>-5.691873585751697</v>
       </c>
       <c r="N156" t="n">
-        <v>-2.731347241019788</v>
+        <v>-2.731330880919775</v>
       </c>
       <c r="O156" t="n">
-        <v>96.61080210043393</v>
+        <v>96.61090988923847</v>
       </c>
       <c r="P156" t="n">
-        <v>29.88740491808047</v>
+        <v>29.88743826349917</v>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
@@ -8768,16 +8768,16 @@
         <v>700.071428571429</v>
       </c>
       <c r="M157" t="n">
-        <v>23.39797035673637</v>
+        <v>23.4004290054088</v>
       </c>
       <c r="N157" t="n">
-        <v>-2.145537496352277</v>
+        <v>-2.145528074380257</v>
       </c>
       <c r="O157" t="n">
-        <v>230.3703498460177</v>
+        <v>230.3705905004948</v>
       </c>
       <c r="P157" t="n">
-        <v>69.1299085038161</v>
+        <v>69.12998071980219</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
@@ -8821,16 +8821,16 @@
         <v>694.285714285714</v>
       </c>
       <c r="M158" t="n">
-        <v>-4.050068594122267</v>
+        <v>-4.049994937579912</v>
       </c>
       <c r="N158" t="n">
-        <v>-1.883435926159666</v>
+        <v>-1.883423385186917</v>
       </c>
       <c r="O158" t="n">
-        <v>230.4717868135969</v>
+        <v>230.4720288087613</v>
       </c>
       <c r="P158" t="n">
-        <v>69.68393554235955</v>
+        <v>69.68400871042785</v>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
@@ -8874,16 +8874,16 @@
         <v>690.428571428571</v>
       </c>
       <c r="M159" t="n">
-        <v>-7.657860292565352</v>
+        <v>-7.658189476042374</v>
       </c>
       <c r="N159" t="n">
-        <v>-3.199034760375794</v>
+        <v>-3.199001595584367</v>
       </c>
       <c r="O159" t="n">
-        <v>239.6653524368402</v>
+        <v>239.6656124179611</v>
       </c>
       <c r="P159" t="n">
-        <v>72.14321343720687</v>
+        <v>72.14329169580077</v>
       </c>
       <c r="Q159" t="n">
         <v>0</v>
@@ -8927,16 +8927,16 @@
         <v>261</v>
       </c>
       <c r="M160" t="n">
-        <v>13.70682735041265</v>
+        <v>13.70684304354333</v>
       </c>
       <c r="N160" t="n">
-        <v>-8.868196430550981</v>
+        <v>-8.867377289249031</v>
       </c>
       <c r="O160" t="n">
-        <v>-17.73639286110258</v>
+        <v>-17.73475457849868</v>
       </c>
       <c r="P160" t="n">
-        <v>-65.46453337274768</v>
+        <v>-65.45848651716454</v>
       </c>
       <c r="Q160" t="n">
         <v>1</v>
@@ -8980,16 +8980,16 @@
         <v>270</v>
       </c>
       <c r="M161" t="n">
-        <v>12.72465821036014</v>
+        <v>12.72467178219338</v>
       </c>
       <c r="N161" t="n">
-        <v>-16.54814130106849</v>
+        <v>-16.54710409067912</v>
       </c>
       <c r="O161" t="n">
-        <v>-294.8713448239581</v>
+        <v>-174.7991655562957</v>
       </c>
       <c r="P161" t="n">
-        <v>-69.84179772059839</v>
+        <v>-69.83413698202162</v>
       </c>
       <c r="Q161" t="n">
         <v>1</v>
@@ -9033,16 +9033,16 @@
         <v>259.2</v>
       </c>
       <c r="M162" t="n">
-        <v>14.00744091156434</v>
+        <v>14.0074573577015</v>
       </c>
       <c r="N162" t="n">
-        <v>4.679092256102408</v>
+        <v>4.68000467909217</v>
       </c>
       <c r="O162" t="n">
-        <v>37.43273804881906</v>
+        <v>37.44003743273716</v>
       </c>
       <c r="P162" t="n">
-        <v>182.4845979879904</v>
+        <v>182.5201824845911</v>
       </c>
       <c r="Q162" t="n">
         <v>1</v>
@@ -9086,16 +9086,16 @@
         <v>153</v>
       </c>
       <c r="M163" t="n">
-        <v>-9.360495716108025</v>
+        <v>-9.359968800630956</v>
       </c>
       <c r="N163" t="n">
-        <v>13.56135081985974</v>
+        <v>13.56136584520744</v>
       </c>
       <c r="O163" t="n">
-        <v>-134.7701186777803</v>
+        <v>-134.785886986652</v>
       </c>
       <c r="P163" t="n">
-        <v>-34.55044208446634</v>
+        <v>-34.5544845387417</v>
       </c>
       <c r="Q163" t="n">
         <v>1</v>
@@ -9139,16 +9139,16 @@
         <v>147.6</v>
       </c>
       <c r="M164" t="n">
-        <v>-3.828701338826337</v>
+        <v>-3.829054010581412</v>
       </c>
       <c r="N164" t="n">
-        <v>14.93264502223738</v>
+        <v>14.9326631333432</v>
       </c>
       <c r="O164" t="n">
-        <v>379.1487681078233</v>
+        <v>379.0655955905328</v>
       </c>
       <c r="P164" t="n">
-        <v>-124.1887747390208</v>
+        <v>-124.1615318890287</v>
       </c>
       <c r="Q164" t="n">
         <v>1</v>
@@ -9192,16 +9192,16 @@
         <v>142.2</v>
       </c>
       <c r="M165" t="n">
-        <v>8.42448769343679</v>
+        <v>8.423918625515224</v>
       </c>
       <c r="N165" t="n">
-        <v>15.25726121083102</v>
+        <v>15.2572808849425</v>
       </c>
       <c r="O165" t="n">
-        <v>-41.09131298254342</v>
+        <v>-41.09307190607523</v>
       </c>
       <c r="P165" t="n">
-        <v>-17.80623562576877</v>
+        <v>-17.80699782596589</v>
       </c>
       <c r="Q165" t="n">
         <v>1</v>
@@ -9245,16 +9245,16 @@
         <v>447.1875</v>
       </c>
       <c r="M166" t="n">
-        <v>19.22609678698989</v>
+        <v>19.22612597173919</v>
       </c>
       <c r="N166" t="n">
-        <v>20.87902868490934</v>
+        <v>20.87906226350391</v>
       </c>
       <c r="O166" t="n">
-        <v>-31.85226262438893</v>
+        <v>-31.85196597053787</v>
       </c>
       <c r="P166" t="n">
-        <v>-14.174024029676</v>
+        <v>-14.1738920208808</v>
       </c>
       <c r="Q166" t="n">
         <v>1</v>
@@ -9298,16 +9298,16 @@
         <v>442.125</v>
       </c>
       <c r="M167" t="n">
-        <v>19.70804815163318</v>
+        <v>19.70807853741923</v>
       </c>
       <c r="N167" t="n">
-        <v>20.16116333202126</v>
+        <v>20.16119491498453</v>
       </c>
       <c r="O167" t="n">
-        <v>-16.14198595469734</v>
+        <v>-16.1418050098854</v>
       </c>
       <c r="P167" t="n">
-        <v>-14.04016486684613</v>
+        <v>-14.04000748255658</v>
       </c>
       <c r="Q167" t="n">
         <v>1</v>
@@ -9351,16 +9351,16 @@
         <v>253.125</v>
       </c>
       <c r="M168" t="n">
-        <v>19.90741130367146</v>
+        <v>19.9074648258233</v>
       </c>
       <c r="N168" t="n">
-        <v>16.99954160589685</v>
+        <v>16.99958250962242</v>
       </c>
       <c r="O168" t="n">
-        <v>-45.6909839168662</v>
+        <v>-45.68953419625194</v>
       </c>
       <c r="P168" t="n">
-        <v>-38.13531339936359</v>
+        <v>-38.13410341119466</v>
       </c>
       <c r="Q168" t="n">
         <v>1</v>
@@ -9404,16 +9404,16 @@
         <v>156.6</v>
       </c>
       <c r="M169" t="n">
-        <v>-1.531626353764529</v>
+        <v>-1.531635759327035</v>
       </c>
       <c r="N169" t="n">
-        <v>12.03315580095588</v>
+        <v>12.03416141758409</v>
       </c>
       <c r="O169" t="n">
-        <v>153.0069813613807</v>
+        <v>153.0074380401964</v>
       </c>
       <c r="P169" t="n">
-        <v>55.16099065361253</v>
+        <v>55.161155292217</v>
       </c>
       <c r="Q169" t="n">
         <v>1</v>
@@ -9457,16 +9457,16 @@
         <v>172.8</v>
       </c>
       <c r="M170" t="n">
-        <v>-3.555605152375199</v>
+        <v>-3.555581758156768</v>
       </c>
       <c r="N170" t="n">
-        <v>7.022202513819519</v>
+        <v>7.020148478194766</v>
       </c>
       <c r="O170" t="n">
-        <v>147.3853978432012</v>
+        <v>147.3858184305572</v>
       </c>
       <c r="P170" t="n">
-        <v>50.50963332219372</v>
+        <v>50.50977745935685</v>
       </c>
       <c r="Q170" t="n">
         <v>1</v>
@@ -9513,13 +9513,13 @@
         <v>-0</v>
       </c>
       <c r="N171" t="n">
-        <v>-7.019850577466314</v>
+        <v>-7.019997241997308</v>
       </c>
       <c r="O171" t="n">
-        <v>137.2208401575522</v>
+        <v>137.2212188092595</v>
       </c>
       <c r="P171" t="n">
-        <v>46.39518431967852</v>
+        <v>46.39531234407871</v>
       </c>
       <c r="Q171" t="n">
         <v>1</v>
@@ -9563,16 +9563,16 @@
         <v>347.4</v>
       </c>
       <c r="M172" t="n">
-        <v>-3.239749754321738</v>
+        <v>-3.240002267748987</v>
       </c>
       <c r="N172" t="n">
-        <v>-1.90667870228173</v>
+        <v>-1.906664931850736</v>
       </c>
       <c r="O172" t="n">
-        <v>307.5421918265821</v>
+        <v>307.5430485509358</v>
       </c>
       <c r="P172" t="n">
-        <v>111.7700439184241</v>
+        <v>111.7703552777146</v>
       </c>
       <c r="Q172" t="n">
         <v>1</v>
@@ -9616,16 +9616,16 @@
         <v>358.2</v>
       </c>
       <c r="M173" t="n">
-        <v>-19.14717631128491</v>
+        <v>-19.14541260135962</v>
       </c>
       <c r="N173" t="n">
-        <v>-3.174901253221699</v>
+        <v>-3.174873253502279</v>
       </c>
       <c r="O173" t="n">
-        <v>332.3902165480145</v>
+        <v>332.391205267536</v>
       </c>
       <c r="P173" t="n">
-        <v>119.3991918334524</v>
+        <v>119.399546995265</v>
       </c>
       <c r="Q173" t="n">
         <v>1</v>
@@ -9669,16 +9669,16 @@
         <v>360</v>
       </c>
       <c r="M174" t="n">
-        <v>18.42626618905179</v>
+        <v>18.42743308421637</v>
       </c>
       <c r="N174" t="n">
-        <v>-115.8833324066381</v>
+        <v>-115.8324875534729</v>
       </c>
       <c r="O174" t="n">
-        <v>340.4570442303683</v>
+        <v>340.4580779706918</v>
       </c>
       <c r="P174" t="n">
-        <v>113.6354734410935</v>
+        <v>113.6358184760196</v>
       </c>
       <c r="Q174" t="n">
         <v>1</v>
@@ -9722,16 +9722,16 @@
         <v>738</v>
       </c>
       <c r="M175" t="n">
-        <v>-4.833364080806518</v>
+        <v>-4.833444366079995</v>
       </c>
       <c r="N175" t="n">
-        <v>-4.680159624644234</v>
+        <v>-4.679977099494548</v>
       </c>
       <c r="O175" t="n">
-        <v>675.0087664582578</v>
+        <v>675.01068335073</v>
       </c>
       <c r="P175" t="n">
-        <v>235.5991573042818</v>
+        <v>235.5998263596682</v>
       </c>
       <c r="Q175" t="n">
         <v>1</v>
@@ -9775,16 +9775,16 @@
         <v>747</v>
       </c>
       <c r="M176" t="n">
-        <v>-14.74278752264786</v>
+        <v>-14.74204061506874</v>
       </c>
       <c r="N176" t="n">
-        <v>2.448888633116191</v>
+        <v>2.448838658723201</v>
       </c>
       <c r="O176" t="n">
-        <v>627.7388002844006</v>
+        <v>627.7404594423467</v>
       </c>
       <c r="P176" t="n">
-        <v>220.1286514246204</v>
+        <v>220.1292332401797</v>
       </c>
       <c r="Q176" t="n">
         <v>1</v>
@@ -9828,16 +9828,16 @@
         <v>689.4</v>
       </c>
       <c r="M177" t="n">
-        <v>-7.020245954252005</v>
+        <v>-7.020008845448197</v>
       </c>
       <c r="N177" t="n">
-        <v>0.3143322404467114</v>
+        <v>0.3143281236398558</v>
       </c>
       <c r="O177" t="n">
-        <v>552.0910631988122</v>
+        <v>552.0924533267162</v>
       </c>
       <c r="P177" t="n">
-        <v>191.7906098760103</v>
+        <v>191.791092791776</v>
       </c>
       <c r="Q177" t="n">
         <v>1</v>
